--- a/outputs/monitor_xlsx/20260203.xlsx
+++ b/outputs/monitor_xlsx/20260203.xlsx
@@ -1176,7 +1176,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -1209,13 +1209,13 @@
           <t>個股籌碼監控報告 - 20260203</t>
         </is>
       </c>
-      <c r="P1" s="15" t="n"/>
-      <c r="Q1" s="16" t="n"/>
-      <c r="R1" s="15" t="n"/>
+      <c r="O1" s="15" t="n"/>
+      <c r="P1" s="16" t="n"/>
+      <c r="Q1" s="15" t="n"/>
+      <c r="R1" s="16" t="n"/>
       <c r="S1" s="16" t="n"/>
       <c r="T1" s="16" t="n"/>
-      <c r="U1" s="16" t="n"/>
-      <c r="V1" s="14" t="n"/>
+      <c r="U1" s="14" t="n"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="14" t="n"/>
@@ -1232,14 +1232,13 @@
       <c r="L2" s="15" t="n"/>
       <c r="M2" s="15" t="n"/>
       <c r="N2" s="16" t="n"/>
-      <c r="O2" s="14" t="n"/>
-      <c r="P2" s="15" t="n"/>
-      <c r="Q2" s="16" t="n"/>
-      <c r="R2" s="15" t="n"/>
+      <c r="O2" s="15" t="n"/>
+      <c r="P2" s="16" t="n"/>
+      <c r="Q2" s="15" t="n"/>
+      <c r="R2" s="16" t="n"/>
       <c r="S2" s="16" t="n"/>
       <c r="T2" s="16" t="n"/>
-      <c r="U2" s="16" t="n"/>
-      <c r="V2" s="14" t="n"/>
+      <c r="U2" s="14" t="n"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -1312,42 +1311,37 @@
           <t>MA20乖離(%)</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>籌碼評價</t>
-        </is>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>買賣券商差</t>
         </is>
       </c>
-      <c r="Q3" s="7" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>籌碼集中度5D(%)</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>借券賣出餘額</t>
         </is>
       </c>
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>短回補天數</t>
+        </is>
+      </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="T3" s="7" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
-        </is>
-      </c>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
           <t>VWAP乖離(%)</t>
         </is>
       </c>
-      <c r="V3" s="5" t="inlineStr">
+      <c r="U3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1398,30 +1392,25 @@
       <c r="N4" s="8" t="n">
         <v>-0.1</v>
       </c>
-      <c r="O4" s="14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="P4" s="10" t="n">
+      <c r="O4" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="P4" s="9" t="n">
         <v>-6.38</v>
       </c>
-      <c r="R4" s="10" t="n">
+      <c r="Q4" s="10" t="n">
         <v>137857000</v>
       </c>
+      <c r="R4" s="8" t="n">
+        <v>0.99</v>
+      </c>
       <c r="S4" s="8" t="n">
-        <v>0.99</v>
+        <v>71.73</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>71.73</v>
-      </c>
-      <c r="U4" s="8" t="n">
         <v>1.7</v>
       </c>
-      <c r="V4" s="14" t="inlineStr">
+      <c r="U4" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1464,30 +1453,25 @@
         <v>-27018</v>
       </c>
       <c r="N5" s="16" t="n"/>
-      <c r="O5" s="14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="P5" s="10" t="n">
+      <c r="O5" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="Q5" s="13" t="n">
+      <c r="P5" s="13" t="n">
         <v>5.02</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="Q5" s="10" t="n">
         <v>1998000</v>
       </c>
+      <c r="R5" s="8" t="n">
+        <v>28.83</v>
+      </c>
       <c r="S5" s="8" t="n">
-        <v>28.83</v>
-      </c>
-      <c r="T5" s="8" t="n">
         <v>114.39</v>
       </c>
-      <c r="U5" s="10" t="n">
+      <c r="T5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="14" t="inlineStr">
+      <c r="U5" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1540,30 +1524,25 @@
       <c r="N6" s="8" t="n">
         <v>-4.96</v>
       </c>
-      <c r="O6" s="14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="P6" s="10" t="n">
+      <c r="O6" s="10" t="n">
         <v>-47</v>
       </c>
-      <c r="Q6" s="13" t="n">
+      <c r="P6" s="13" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="Q6" s="10" t="n">
         <v>3543000</v>
       </c>
+      <c r="R6" s="8" t="n">
+        <v>0.99</v>
+      </c>
       <c r="S6" s="8" t="n">
-        <v>0.99</v>
+        <v>932.15</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>932.15</v>
-      </c>
-      <c r="U6" s="8" t="n">
         <v>1.59</v>
       </c>
-      <c r="V6" s="14" t="inlineStr">
+      <c r="U6" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1616,30 +1595,25 @@
       <c r="N7" s="8" t="n">
         <v>-12.96</v>
       </c>
-      <c r="O7" s="14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="P7" s="10" t="n">
+      <c r="O7" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="P7" s="9" t="n">
         <v>-7.31</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="Q7" s="10" t="n">
         <v>175067918</v>
       </c>
+      <c r="R7" s="8" t="n">
+        <v>0.73</v>
+      </c>
       <c r="S7" s="8" t="n">
-        <v>0.73</v>
+        <v>41.21</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>41.21</v>
-      </c>
-      <c r="U7" s="8" t="n">
         <v>-11.19</v>
       </c>
-      <c r="V7" s="14" t="inlineStr">
+      <c r="U7" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1692,30 +1666,25 @@
       <c r="N8" s="8" t="n">
         <v>-1.7</v>
       </c>
-      <c r="O8" s="14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="P8" s="10" t="n">
+      <c r="O8" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="P8" s="9" t="n">
         <v>-4.17</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="Q8" s="10" t="n">
         <v>2189680</v>
       </c>
+      <c r="R8" s="8" t="n">
+        <v>0.19</v>
+      </c>
       <c r="S8" s="8" t="n">
-        <v>0.19</v>
+        <v>1149.53</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>1149.53</v>
-      </c>
-      <c r="U8" s="8" t="n">
         <v>5.7</v>
       </c>
-      <c r="V8" s="14" t="inlineStr">
+      <c r="U8" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1768,30 +1737,25 @@
       <c r="N9" s="8" t="n">
         <v>0.61</v>
       </c>
-      <c r="O9" s="14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="P9" s="10" t="n">
+      <c r="O9" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="P9" s="9" t="n">
         <v>-8.98</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="Q9" s="10" t="n">
         <v>1553680</v>
       </c>
+      <c r="R9" s="8" t="n">
+        <v>0.04</v>
+      </c>
       <c r="S9" s="8" t="n">
-        <v>0.04</v>
+        <v>1739.86</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>1739.86</v>
-      </c>
-      <c r="U9" s="8" t="n">
         <v>3.46</v>
       </c>
-      <c r="V9" s="14" t="inlineStr">
+      <c r="U9" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1844,30 +1808,25 @@
       <c r="N10" s="8" t="n">
         <v>-14.51</v>
       </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="P10" s="10" t="n">
+      <c r="O10" s="10" t="n">
         <v>-15</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="P10" s="9" t="n">
         <v>-6.72</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="Q10" s="10" t="n">
         <v>30740000</v>
       </c>
+      <c r="R10" s="8" t="n">
+        <v>0.12</v>
+      </c>
       <c r="S10" s="8" t="n">
-        <v>0.12</v>
+        <v>115.13</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>115.13</v>
-      </c>
-      <c r="U10" s="8" t="n">
         <v>-8.359999999999999</v>
       </c>
-      <c r="V10" s="14" t="inlineStr">
+      <c r="U10" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1920,30 +1879,25 @@
       <c r="N11" s="8" t="n">
         <v>2.6</v>
       </c>
-      <c r="O11" s="14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="P11" s="10" t="n">
+      <c r="O11" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="P11" s="9" t="n">
         <v>-2.55</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="Q11" s="10" t="n">
         <v>1817528</v>
       </c>
+      <c r="R11" s="8" t="n">
+        <v>0.47</v>
+      </c>
       <c r="S11" s="8" t="n">
-        <v>0.47</v>
+        <v>1681.45</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>1681.45</v>
-      </c>
-      <c r="U11" s="8" t="n">
         <v>10.32</v>
       </c>
-      <c r="V11" s="14" t="inlineStr">
+      <c r="U11" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -1996,30 +1950,25 @@
       <c r="N12" s="8" t="n">
         <v>1.62</v>
       </c>
-      <c r="O12" s="14" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="P12" s="10" t="n">
+      <c r="O12" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="P12" s="9" t="n">
         <v>-3.98</v>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="Q12" s="10" t="n">
         <v>5343503</v>
       </c>
+      <c r="R12" s="8" t="n">
+        <v>2.2</v>
+      </c>
       <c r="S12" s="8" t="n">
-        <v>2.2</v>
+        <v>3418.66</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>3418.66</v>
-      </c>
-      <c r="U12" s="8" t="n">
         <v>-2.89</v>
       </c>
-      <c r="V12" s="14" t="inlineStr">
+      <c r="U12" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2072,30 +2021,25 @@
       <c r="N13" s="8" t="n">
         <v>0.72</v>
       </c>
-      <c r="O13" s="14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="P13" s="10" t="n">
+      <c r="O13" s="10" t="n">
         <v>-6</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="P13" s="9" t="n">
         <v>-6.36</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="Q13" s="10" t="n">
         <v>21769945</v>
       </c>
+      <c r="R13" s="8" t="n">
+        <v>0.53</v>
+      </c>
       <c r="S13" s="8" t="n">
-        <v>0.53</v>
+        <v>173.89</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>173.89</v>
-      </c>
-      <c r="U13" s="8" t="n">
         <v>4.09</v>
       </c>
-      <c r="V13" s="14" t="inlineStr">
+      <c r="U13" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2148,30 +2092,25 @@
       <c r="N14" s="8" t="n">
         <v>11.31</v>
       </c>
-      <c r="O14" s="14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="P14" s="10" t="n">
+      <c r="O14" s="10" t="n">
         <v>-23</v>
       </c>
-      <c r="Q14" s="13" t="n">
+      <c r="P14" s="13" t="n">
         <v>7.52</v>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="Q14" s="10" t="n">
         <v>1868000</v>
       </c>
+      <c r="R14" s="8" t="n">
+        <v>0.43</v>
+      </c>
       <c r="S14" s="8" t="n">
-        <v>0.43</v>
+        <v>1465.5</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>1465.5</v>
-      </c>
-      <c r="U14" s="8" t="n">
         <v>24.87</v>
       </c>
-      <c r="V14" s="14" t="inlineStr">
+      <c r="U14" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2222,30 +2161,25 @@
       <c r="N15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="14" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="n">
+      <c r="O15" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="Q15" s="13" t="n">
+      <c r="P15" s="13" t="n">
         <v>5.83</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="Q15" s="10" t="n">
         <v>2209400</v>
       </c>
+      <c r="R15" s="8" t="n">
+        <v>2.45</v>
+      </c>
       <c r="S15" s="8" t="n">
-        <v>2.45</v>
+        <v>771.6900000000001</v>
       </c>
       <c r="T15" s="8" t="n">
-        <v>771.6900000000001</v>
-      </c>
-      <c r="U15" s="8" t="n">
         <v>41.9</v>
       </c>
-      <c r="V15" s="14" t="inlineStr">
+      <c r="U15" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2298,30 +2232,25 @@
       <c r="N16" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="P16" s="10" t="n">
+      <c r="O16" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Q16" s="13" t="n">
+      <c r="P16" s="13" t="n">
         <v>6.72</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="Q16" s="10" t="n">
         <v>7790640</v>
       </c>
+      <c r="R16" s="8" t="n">
+        <v>0.33</v>
+      </c>
       <c r="S16" s="8" t="n">
-        <v>0.33</v>
+        <v>335.61</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>335.61</v>
-      </c>
-      <c r="U16" s="8" t="n">
         <v>-6.89</v>
       </c>
-      <c r="V16" s="14" t="inlineStr">
+      <c r="U16" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2372,30 +2301,25 @@
       <c r="N17" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="14" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="P17" s="10" t="n">
+      <c r="O17" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="P17" s="9" t="n">
         <v>-1.97</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="Q17" s="10" t="n">
         <v>2204000</v>
       </c>
+      <c r="R17" s="8" t="n">
+        <v>1.72</v>
+      </c>
       <c r="S17" s="8" t="n">
-        <v>1.72</v>
+        <v>139.79</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>139.79</v>
-      </c>
-      <c r="U17" s="8" t="n">
         <v>-2.71</v>
       </c>
-      <c r="V17" s="14" t="inlineStr">
+      <c r="U17" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2448,30 +2372,25 @@
       <c r="N18" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="14" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="P18" s="10" t="n">
+      <c r="O18" s="10" t="n">
         <v>-46</v>
       </c>
-      <c r="Q18" s="13" t="n">
+      <c r="P18" s="13" t="n">
         <v>9.68</v>
       </c>
-      <c r="R18" s="10" t="n">
+      <c r="Q18" s="10" t="n">
         <v>11417993</v>
       </c>
+      <c r="R18" s="8" t="n">
+        <v>0.39</v>
+      </c>
       <c r="S18" s="8" t="n">
-        <v>0.39</v>
+        <v>303.31</v>
       </c>
       <c r="T18" s="8" t="n">
-        <v>303.31</v>
-      </c>
-      <c r="U18" s="8" t="n">
         <v>3.52</v>
       </c>
-      <c r="V18" s="14" t="inlineStr">
+      <c r="U18" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2524,30 +2443,25 @@
       <c r="N19" s="8" t="n">
         <v>3.1</v>
       </c>
-      <c r="O19" s="14" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="P19" s="10" t="n">
+      <c r="O19" s="10" t="n">
         <v>-30</v>
       </c>
-      <c r="Q19" s="13" t="n">
+      <c r="P19" s="13" t="n">
         <v>0.32</v>
       </c>
-      <c r="R19" s="10" t="n">
+      <c r="Q19" s="10" t="n">
         <v>10991826</v>
       </c>
+      <c r="R19" s="8" t="n">
+        <v>0.21</v>
+      </c>
       <c r="S19" s="8" t="n">
-        <v>0.21</v>
+        <v>209.7</v>
       </c>
       <c r="T19" s="8" t="n">
-        <v>209.7</v>
-      </c>
-      <c r="U19" s="8" t="n">
         <v>17.31</v>
       </c>
-      <c r="V19" s="14" t="inlineStr">
+      <c r="U19" s="14" t="inlineStr">
         <is>
           <t>partial</t>
         </is>
@@ -2600,11 +2514,6 @@
       <c r="N20" t="n">
         <v>-2.59</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2653,11 +2562,6 @@
       <c r="N21" t="n">
         <v>4.46</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2706,11 +2610,6 @@
       <c r="N22" t="n">
         <v>-7.35</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2759,11 +2658,6 @@
       <c r="N23" t="n">
         <v>0.83</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2812,11 +2706,6 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2865,11 +2754,6 @@
       <c r="N25" t="n">
         <v>0</v>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2918,11 +2802,6 @@
       <c r="N26" t="n">
         <v>3.15</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2970,11 +2849,6 @@
       </c>
       <c r="N27" t="n">
         <v>6.86</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260203.xlsx
+++ b/outputs/monitor_xlsx/20260203.xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -199,6 +199,15 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1176,7 +1185,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
@@ -1209,7 +1218,6 @@
           <t>個股籌碼監控報告 - 20260203</t>
         </is>
       </c>
-      <c r="O1" s="15" t="n"/>
       <c r="P1" s="16" t="n"/>
       <c r="Q1" s="15" t="n"/>
       <c r="R1" s="16" t="n"/>
@@ -1355,45 +1363,49 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="n">
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="n">
         <v>72.95</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="E4" s="24" t="n">
         <v>2.03</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="F4" s="24" t="n">
         <v>73734</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="G4" s="24" t="n">
         <v>-414</v>
       </c>
-      <c r="G4" s="10" t="n">
-        <v>-164720</v>
-      </c>
-      <c r="H4" s="15" t="n"/>
+      <c r="H4" s="15" t="n">
+        <v>-168863</v>
+      </c>
       <c r="I4" s="10" t="n">
-        <v>1911</v>
+        <v>0</v>
       </c>
       <c r="J4" s="10" t="n">
+        <v>1629</v>
+      </c>
+      <c r="K4" s="10" t="n">
         <v>13688</v>
       </c>
-      <c r="K4" s="10" t="n">
+      <c r="L4" s="10" t="n">
         <v>7650</v>
       </c>
-      <c r="L4" s="10" t="n">
-        <v>36283</v>
-      </c>
       <c r="M4" s="10" t="n">
+        <v>36987</v>
+      </c>
+      <c r="N4" s="8" t="n">
         <v>-4010833</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="O4" s="10" t="n">
-        <v>33</v>
+        <v>1.48</v>
       </c>
       <c r="P4" s="9" t="n">
         <v>-6.38</v>
@@ -1488,44 +1500,46 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n">
         <v>947</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="E6" s="24" t="n">
         <v>0.53</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="F6" s="24" t="n">
         <v>5962</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="G6" s="24" t="n">
         <v>-920</v>
       </c>
-      <c r="G6" s="10" t="n">
-        <v>1481</v>
-      </c>
       <c r="H6" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="I6" s="10" t="n">
         <v>-130</v>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>-302</v>
-      </c>
       <c r="J6" s="10" t="n">
+        <v>-278</v>
+      </c>
+      <c r="K6" s="10" t="n">
         <v>173</v>
       </c>
-      <c r="K6" s="10" t="n">
+      <c r="L6" s="10" t="n">
         <v>2775</v>
       </c>
-      <c r="L6" s="10" t="n">
-        <v>13627</v>
-      </c>
       <c r="M6" s="10" t="n">
+        <v>13618</v>
+      </c>
+      <c r="N6" s="8" t="n">
         <v>-78719</v>
       </c>
-      <c r="N6" s="8" t="n">
-        <v>-4.96</v>
-      </c>
       <c r="O6" s="10" t="n">
-        <v>-47</v>
+        <v>0.14</v>
       </c>
       <c r="P6" s="13" t="n">
         <v>8.369999999999999</v>
@@ -1630,44 +1644,46 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="n">
         <v>1215</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="E8" s="24" t="n">
         <v>3.4</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="F8" s="24" t="n">
         <v>11407</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="G8" s="24" t="n">
         <v>-1110</v>
       </c>
-      <c r="G8" s="10" t="n">
-        <v>138</v>
-      </c>
       <c r="H8" s="10" t="n">
+        <v>-932</v>
+      </c>
+      <c r="I8" s="10" t="n">
         <v>-41</v>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>-338</v>
-      </c>
       <c r="J8" s="10" t="n">
+        <v>-762</v>
+      </c>
+      <c r="K8" s="10" t="n">
         <v>424</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="L8" s="10" t="n">
         <v>6283</v>
       </c>
-      <c r="L8" s="10" t="n">
-        <v>34689</v>
-      </c>
       <c r="M8" s="10" t="n">
+        <v>32845</v>
+      </c>
+      <c r="N8" s="8" t="n">
         <v>-648628</v>
       </c>
-      <c r="N8" s="8" t="n">
-        <v>-1.7</v>
-      </c>
       <c r="O8" s="10" t="n">
-        <v>41</v>
+        <v>5.63</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>-4.17</v>
@@ -1701,44 +1717,46 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="n">
         <v>1800</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="E9" s="24" t="n">
         <v>1.98</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="F9" s="24" t="n">
         <v>30386</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="G9" s="24" t="n">
         <v>-2924</v>
       </c>
-      <c r="G9" s="10" t="n">
-        <v>-17775</v>
-      </c>
       <c r="H9" s="10" t="n">
+        <v>-27402</v>
+      </c>
+      <c r="I9" s="10" t="n">
         <v>1083</v>
       </c>
-      <c r="I9" s="10" t="n">
-        <v>2890</v>
-      </c>
       <c r="J9" s="10" t="n">
+        <v>4257</v>
+      </c>
+      <c r="K9" s="10" t="n">
         <v>394</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="L9" s="10" t="n">
         <v>21879</v>
       </c>
-      <c r="L9" s="10" t="n">
-        <v>100916</v>
-      </c>
       <c r="M9" s="10" t="n">
+        <v>103004</v>
+      </c>
+      <c r="N9" s="8" t="n">
         <v>-6482876</v>
       </c>
-      <c r="N9" s="8" t="n">
-        <v>0.61</v>
-      </c>
       <c r="O9" s="10" t="n">
-        <v>13</v>
+        <v>2.98</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>-8.98</v>
@@ -1843,44 +1861,46 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="n">
         <v>1855</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="E11" s="24" t="n">
         <v>3.92</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="F11" s="25" t="n">
         <v>4101</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="25" t="n">
         <v>124</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>924</v>
-      </c>
       <c r="H11" s="10" t="n">
+        <v>132</v>
+      </c>
+      <c r="I11" s="10" t="n">
         <v>106</v>
       </c>
-      <c r="I11" s="10" t="n">
-        <v>92</v>
-      </c>
       <c r="J11" s="10" t="n">
+        <v>214</v>
+      </c>
+      <c r="K11" s="10" t="n">
         <v>89</v>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="L11" s="10" t="n">
         <v>2093</v>
       </c>
-      <c r="L11" s="10" t="n">
-        <v>9970</v>
-      </c>
       <c r="M11" s="10" t="n">
+        <v>10070</v>
+      </c>
+      <c r="N11" s="8" t="n">
         <v>-89490</v>
       </c>
-      <c r="N11" s="8" t="n">
-        <v>2.6</v>
-      </c>
       <c r="O11" s="10" t="n">
-        <v>39</v>
+        <v>9.9</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>-2.55</v>
@@ -2056,44 +2076,46 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="n">
         <v>1830</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="E14" s="24" t="n">
         <v>7.02</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="F14" s="24" t="n">
         <v>5927</v>
       </c>
-      <c r="F14" s="11" t="n">
+      <c r="G14" s="24" t="n">
         <v>-275</v>
       </c>
-      <c r="G14" s="10" t="n">
-        <v>3270</v>
-      </c>
       <c r="H14" s="10" t="n">
+        <v>2826</v>
+      </c>
+      <c r="I14" s="10" t="n">
         <v>133</v>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>-220</v>
-      </c>
       <c r="J14" s="10" t="n">
+        <v>-82</v>
+      </c>
+      <c r="K14" s="10" t="n">
         <v>79</v>
       </c>
-      <c r="K14" s="10" t="n">
+      <c r="L14" s="10" t="n">
         <v>4445</v>
       </c>
-      <c r="L14" s="10" t="n">
-        <v>23499</v>
-      </c>
       <c r="M14" s="10" t="n">
+        <v>22736</v>
+      </c>
+      <c r="N14" s="8" t="n">
         <v>-19229</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>11.31</v>
-      </c>
       <c r="O14" s="10" t="n">
-        <v>-23</v>
+        <v>27.95</v>
       </c>
       <c r="P14" s="13" t="n">
         <v>7.52</v>
@@ -2127,42 +2149,46 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C15" s="10" t="n">
-        <v>1095</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>903</v>
-      </c>
-      <c r="F15" s="12" t="n">
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>2365</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G15" s="25" t="n">
         <v>424</v>
       </c>
-      <c r="G15" s="10" t="n">
-        <v>1389</v>
-      </c>
-      <c r="H15" s="15" t="n"/>
+      <c r="H15" s="15" t="n">
+        <v>2896</v>
+      </c>
       <c r="I15" s="10" t="n">
-        <v>935</v>
+        <v>0</v>
       </c>
       <c r="J15" s="10" t="n">
+        <v>686</v>
+      </c>
+      <c r="K15" s="10" t="n">
         <v>88</v>
       </c>
-      <c r="K15" s="10" t="n">
+      <c r="L15" s="10" t="n">
         <v>-123</v>
       </c>
-      <c r="L15" s="10" t="n">
-        <v>-1064</v>
-      </c>
       <c r="M15" s="10" t="n">
-        <v>0</v>
+        <v>-1493</v>
       </c>
       <c r="N15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="P15" s="13" t="n">
         <v>5.83</v>
@@ -2336,44 +2362,46 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n">
-        <v>314</v>
-      </c>
-      <c r="D18" s="13" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>29576</v>
-      </c>
-      <c r="F18" s="11" t="n">
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>586</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>32773</v>
+      </c>
+      <c r="G18" s="24" t="n">
         <v>-1860</v>
       </c>
-      <c r="G18" s="10" t="n">
-        <v>2980</v>
-      </c>
       <c r="H18" s="10" t="n">
+        <v>808</v>
+      </c>
+      <c r="I18" s="10" t="n">
         <v>254</v>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>6138</v>
-      </c>
       <c r="J18" s="10" t="n">
+        <v>6380</v>
+      </c>
+      <c r="K18" s="10" t="n">
         <v>-86</v>
       </c>
-      <c r="K18" s="10" t="n">
+      <c r="L18" s="10" t="n">
         <v>310</v>
       </c>
-      <c r="L18" s="10" t="n">
-        <v>-2651</v>
-      </c>
       <c r="M18" s="10" t="n">
-        <v>0</v>
+        <v>-2547</v>
       </c>
       <c r="N18" s="10" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="10" t="n">
-        <v>-46</v>
+        <v>0</v>
       </c>
       <c r="P18" s="13" t="n">
         <v>9.68</v>
@@ -2622,41 +2650,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n">
         <v>1185</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="E23" s="22" t="n">
         <v>3.95</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" s="21" t="n">
         <v>5512</v>
       </c>
-      <c r="F23" s="21" t="n">
+      <c r="G23" s="21" t="n">
         <v>41</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>120</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>236</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>-662</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>97</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>2626</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>13278</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-140175</v>
       </c>
-      <c r="N23" t="n">
-        <v>0.83</v>
+      <c r="O23" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="24">
@@ -2670,42 +2703,47 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>962</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D24" s="21" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F24" s="22" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G24" s="22" t="n">
         <v>-77</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>177</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>6</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-4</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>-158</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2718,42 +2756,47 @@
           <t>萬潤</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>624</v>
-      </c>
-      <c r="D25" s="22" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2040</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>-2.64</v>
       </c>
       <c r="F25" s="22" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G25" s="22" t="n">
         <v>-85</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>100</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>-6</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>-45</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-17</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2766,41 +2809,46 @@
           <t>致茂</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="n">
         <v>1040</v>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="E26" s="22" t="n">
         <v>7.11</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" s="22" t="n">
         <v>3193</v>
       </c>
-      <c r="F26" s="22" t="n">
+      <c r="G26" s="22" t="n">
         <v>-60</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>-99</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>161</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>290</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>56</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>924</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>4564</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>-106274</v>
       </c>
-      <c r="N26" t="n">
-        <v>3.15</v>
+      <c r="O26" t="n">
+        <v>4.93</v>
       </c>
     </row>
     <row r="27">
@@ -2849,6 +2897,112 @@
       </c>
       <c r="N27" t="n">
         <v>6.86</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>4465</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="F28" s="21" t="n">
+        <v>1330</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="H28" t="n">
+        <v>93</v>
+      </c>
+      <c r="I28" t="n">
+        <v>236</v>
+      </c>
+      <c r="J28" t="n">
+        <v>96</v>
+      </c>
+      <c r="K28" t="n">
+        <v>25</v>
+      </c>
+      <c r="L28" t="n">
+        <v>299</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1937</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-8867</v>
+      </c>
+      <c r="O28" t="n">
+        <v>18.77</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F29" s="22" t="n">
+        <v>2696</v>
+      </c>
+      <c r="G29" s="22" t="n">
+        <v>-464</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-2460</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-135</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-43</v>
+      </c>
+      <c r="K29" t="n">
+        <v>50</v>
+      </c>
+      <c r="L29" t="n">
+        <v>5988</v>
+      </c>
+      <c r="M29" t="n">
+        <v>31245</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-21758</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-8.390000000000001</v>
       </c>
     </row>
   </sheetData>
